--- a/config/Excel/Zone_Stage_Waves.xlsx
+++ b/config/Excel/Zone_Stage_Waves.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">地圖識別碼</t>
   </si>
@@ -21,6 +21,9 @@
   </si>
   <si>
     <t xml:space="preserve">出怪間隔秒數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同時上限隻數</t>
   </si>
   <si>
     <t xml:space="preserve">desert</t>
@@ -96,10 +99,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -109,11 +115,14 @@
       </c>
       <c r="D2">
         <v>2</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -123,11 +132,14 @@
       </c>
       <c r="D3">
         <v>2</v>
+      </c>
+      <c r="E3">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -137,11 +149,14 @@
       </c>
       <c r="D4">
         <v>2</v>
+      </c>
+      <c r="E4">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -151,11 +166,14 @@
       </c>
       <c r="D5">
         <v>2</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -165,11 +183,14 @@
       </c>
       <c r="D6">
         <v>2</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -179,11 +200,14 @@
       </c>
       <c r="D7">
         <v>2</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -193,6 +217,9 @@
       </c>
       <c r="D8">
         <v>2</v>
+      </c>
+      <c r="E8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -215,10 +242,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -228,11 +258,14 @@
       </c>
       <c r="D2">
         <v>2</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -242,11 +275,14 @@
       </c>
       <c r="D3">
         <v>2</v>
+      </c>
+      <c r="E3">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -256,11 +292,14 @@
       </c>
       <c r="D4">
         <v>2</v>
+      </c>
+      <c r="E4">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -270,11 +309,14 @@
       </c>
       <c r="D5">
         <v>2</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -284,11 +326,14 @@
       </c>
       <c r="D6">
         <v>2</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -298,11 +343,14 @@
       </c>
       <c r="D7">
         <v>2</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -312,6 +360,9 @@
       </c>
       <c r="D8">
         <v>2</v>
+      </c>
+      <c r="E8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Zone_Stage_Waves.xlsx
+++ b/config/Excel/Zone_Stage_Waves.xlsx
@@ -117,7 +117,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -134,7 +134,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -151,7 +151,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -168,7 +168,7 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -185,7 +185,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -202,7 +202,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -219,7 +219,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -260,7 +260,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -277,7 +277,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -294,7 +294,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -311,7 +311,7 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -328,7 +328,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -345,7 +345,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -362,7 +362,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Zone_Stage_Waves.xlsx
+++ b/config/Excel/Zone_Stage_Waves.xlsx
@@ -114,7 +114,7 @@
         <v>9999</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -131,7 +131,7 @@
         <v>9999</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -148,7 +148,7 @@
         <v>9999</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -165,7 +165,7 @@
         <v>9999</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -182,7 +182,7 @@
         <v>9999</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -199,7 +199,7 @@
         <v>9999</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -216,7 +216,7 @@
         <v>9999</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -257,7 +257,7 @@
         <v>9999</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -274,7 +274,7 @@
         <v>9999</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -291,7 +291,7 @@
         <v>9999</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -308,7 +308,7 @@
         <v>9999</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -325,7 +325,7 @@
         <v>9999</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -342,7 +342,7 @@
         <v>9999</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -359,7 +359,7 @@
         <v>9999</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
